--- a/docs/采购.xlsx
+++ b/docs/采购.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
   <si>
     <t xml:space="preserve">类别</t>
   </si>
@@ -55,31 +55,14 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">应变片</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">采购</t>
-    </r>
+    <t xml:space="preserve">已采购</t>
   </si>
   <si>
     <r>
@@ -94,24 +77,17 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">应变片模块</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">已采购</t>
-  </si>
-  <si>
     <t xml:space="preserve">手套板子</t>
   </si>
   <si>
     <t xml:space="preserve">mpu9250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未采购</t>
   </si>
   <si>
     <t xml:space="preserve">手套电池</t>
@@ -126,60 +102,10 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="DejaVu Sans"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">AR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">显示模块</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">显示驱动板</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">miniHDMI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">转</t>
+      <t xml:space="preserve">影创</t>
     </r>
     <r>
       <rPr>
@@ -188,49 +114,25 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">HDMI</t>
+      <t xml:space="preserve">JIMO AR</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">显示线</t>
+      <t xml:space="preserve">眼镜</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">打印外壳</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">单协白嫖</t>
+    <t xml:space="preserve">郭卓鑫提供</t>
   </si>
   <si>
     <t xml:space="preserve">主控板</t>
   </si>
   <si>
     <t xml:space="preserve">飞腾派</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相机</t>
   </si>
 </sst>
 </file>
@@ -243,9 +145,8 @@
   <fonts count="6">
     <font>
       <sz val="10"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -272,6 +173,7 @@
       <sz val="10"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -338,7 +240,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -468,11 +370,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="10.66796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="10.95703125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -495,7 +397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -508,262 +410,215 @@
       <c r="D2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>2.5</v>
       </c>
       <c r="F2" s="1" t="n">
         <f aca="false">C2*D2+E2</f>
         <v>172.5</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="n">
         <f aca="false">C3*D3+E3</f>
-        <v>101.4</v>
+        <v>144</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>38.63</v>
+        <f aca="false">C4*D4+E4</f>
+        <v>2.66</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>56.9</v>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <f aca="false">38.63+4.17+5.72+4.95+11.1</f>
+        <v>64.57</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="1" t="n">
         <f aca="false">C5*D5+E5</f>
-        <v>113.8</v>
+        <v>64.57</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>9.5</v>
+        <v>54</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="E6" s="1" t="n">
+        <v>4.5</v>
+      </c>
       <c r="F6" s="1" t="n">
         <f aca="false">C6*D6+E6</f>
-        <v>19</v>
+        <v>112.5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <f aca="false">C7*D7+E7</f>
+        <v>19</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="1" t="n">
+        <f aca="false">SUM(F2:F7)</f>
+        <v>515.23</v>
+      </c>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="1" t="n">
-        <f aca="false">SUM(F2:F6)</f>
-        <v>445.33</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="1" t="n">
+        <f aca="false">SUM(F9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>369</v>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <f aca="false">C8*D8+E8</f>
-        <v>238</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>230</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <f aca="false">C9*D9+E9</f>
-        <v>240</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <f aca="false">C10*D10+E10</f>
-        <v>6</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="F11" s="1" t="n">
         <f aca="false">C11*D11+E11</f>
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
+      <c r="A12" s="6"/>
       <c r="B12" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="1" t="n">
-        <f aca="false">SUM(F8:F9)</f>
-        <v>478</v>
-      </c>
+        <f aca="false">SUM(F11)</f>
+        <v>369</v>
+      </c>
+      <c r="G12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>799</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="A13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
       <c r="F13" s="1" t="n">
-        <f aca="false">C13*D13+E13</f>
-        <v>799</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <f aca="false">C14*D14+E14</f>
-        <v>20</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="1" t="n">
-        <f aca="false">SUM(F13:F14)</f>
-        <v>819</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="1" t="n">
-        <f aca="false">SUM(F7+F12+F15)</f>
-        <v>1742.33</v>
+        <f aca="false">SUM(F8+F10+F12)</f>
+        <v>884.23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="A11:A12"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
